--- a/Templates/Tables/MissionInfo/G_MissionInfoTable.xlsx
+++ b/Templates/Tables/MissionInfo/G_MissionInfoTable.xlsx
@@ -24722,9 +24722,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
